--- a/Stock.xlsx
+++ b/Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\PROGRAMACIÓN\ControlStockWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0ACD78-0699-4956-92C3-00126F26B947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983F97D1-748B-434B-850F-20703C7C6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11790,7 +11790,7 @@
         <v>314</v>
       </c>
       <c r="D439">
-        <v>1500</v>
+        <v>150000</v>
       </c>
       <c r="E439">
         <v>0</v>

--- a/Stock.xlsx
+++ b/Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\PROGRAMACIÓN\ControlStockWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983F97D1-748B-434B-850F-20703C7C6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C7530C-D02D-4606-B71A-CA4730F17F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11790,7 +11790,7 @@
         <v>314</v>
       </c>
       <c r="D439">
-        <v>150000</v>
+        <v>15</v>
       </c>
       <c r="E439">
         <v>0</v>

--- a/Stock.xlsx
+++ b/Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\PROGRAMACIÓN\ControlStockWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C7530C-D02D-4606-B71A-CA4730F17F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A7F61B-586A-4613-907C-31CD896E5AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11790,7 +11790,7 @@
         <v>314</v>
       </c>
       <c r="D439">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E439">
         <v>0</v>
